--- a/metadata_dra.xlsx
+++ b/metadata_dra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\1023\submission-excel2xml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\sub2xml-dra-1.6.1\submission-excel2xml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4FED7E-5C56-446F-9B98-77307729F7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00429A0-35B8-41E3-809A-68F3FF0FD23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -420,7 +420,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="214">
   <si>
     <t>Library Source</t>
   </si>
@@ -1082,11 +1082,15 @@
     <t>Sentosa SQ301</t>
   </si>
   <si>
-    <t>v3.1</t>
+    <t>2024-yy-xx Bioinformation and DDBJ Center</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>2024-10-23 Bioinformation and DDBJ Center</t>
+    <t>v3.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X Plus</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1564,12 +1568,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="52.8">
@@ -1725,9 +1729,9 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DF0F4F9-0E4E-4ABA-B02F-964432F322D9}">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$82</xm:f>
+            <xm:f>Admin!$D$2:$D$83</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I3000</xm:sqref>
+          <xm:sqref>I3:I3000 I2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -28255,7 +28259,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -28636,8 +28640,8 @@
       <c r="C19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>63</v>
+      <c r="D19" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -28653,7 +28657,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -28669,7 +28673,7 @@
         <v>57</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -28685,7 +28689,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -28701,7 +28705,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -28717,7 +28721,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -28733,7 +28737,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -28749,7 +28753,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -28765,7 +28769,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -28781,7 +28785,7 @@
         <v>78</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -28797,7 +28801,7 @@
         <v>146</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -28813,7 +28817,7 @@
         <v>81</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -28827,7 +28831,7 @@
         <v>83</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -28841,7 +28845,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -28855,7 +28859,7 @@
         <v>85</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -28869,7 +28873,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -28883,7 +28887,7 @@
         <v>111</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -28897,7 +28901,7 @@
         <v>110</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -28911,7 +28915,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -28925,7 +28929,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -28937,7 +28941,7 @@
       <c r="B39" s="5"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -28949,7 +28953,7 @@
       <c r="B40" s="5"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -28957,212 +28961,217 @@
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="D42" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="D42" s="1" t="s">
+    <row r="43" spans="1:8">
+      <c r="D43" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="D43" s="1" t="s">
+    <row r="44" spans="1:8">
+      <c r="D44" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
-      <c r="D44" s="1" t="s">
+    <row r="45" spans="1:8">
+      <c r="D45" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="D45" s="4" t="s">
+    <row r="46" spans="1:8">
+      <c r="D46" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="D46" s="4" t="s">
+    <row r="47" spans="1:8">
+      <c r="D47" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="D47" s="4" t="s">
+    <row r="48" spans="1:8">
+      <c r="D48" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="D48" s="1" t="s">
+    <row r="49" spans="4:4">
+      <c r="D49" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="1" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="4:4">
-      <c r="D50" s="1" t="s">
+    <row r="51" spans="4:4">
+      <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="4:4">
-      <c r="D51" s="1" t="s">
+    <row r="52" spans="4:4">
+      <c r="D52" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="1" t="s">
+    <row r="53" spans="4:4">
+      <c r="D53" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="4:4">
-      <c r="D53" s="1" t="s">
+    <row r="54" spans="4:4">
+      <c r="D54" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="4:4">
-      <c r="D54" s="1" t="s">
+    <row r="55" spans="4:4">
+      <c r="D55" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="4:4">
-      <c r="D55" s="1" t="s">
+    <row r="56" spans="4:4">
+      <c r="D56" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="4:4">
-      <c r="D56" s="1" t="s">
+    <row r="57" spans="4:4">
+      <c r="D57" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="4:4">
-      <c r="D57" s="1" t="s">
+    <row r="58" spans="4:4">
+      <c r="D58" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="1" t="s">
+    <row r="59" spans="4:4">
+      <c r="D59" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="4:4">
-      <c r="D59" s="1" t="s">
+    <row r="60" spans="4:4">
+      <c r="D60" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="60" spans="4:4">
-      <c r="D60" s="1" t="s">
+    <row r="61" spans="4:4">
+      <c r="D61" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="4:4">
-      <c r="D61" s="1" t="s">
+    <row r="62" spans="4:4">
+      <c r="D62" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="4:4">
-      <c r="D62" s="1" t="s">
+    <row r="63" spans="4:4">
+      <c r="D63" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="4:4">
-      <c r="D63" s="1" t="s">
+    <row r="64" spans="4:4">
+      <c r="D64" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="64" spans="4:4">
-      <c r="D64" s="1" t="s">
+    <row r="65" spans="4:4">
+      <c r="D65" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="4:4">
-      <c r="D65" s="1" t="s">
+    <row r="66" spans="4:4">
+      <c r="D66" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="4:4">
-      <c r="D66" s="1" t="s">
+    <row r="67" spans="4:4">
+      <c r="D67" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="67" spans="4:4">
-      <c r="D67" s="1" t="s">
+    <row r="68" spans="4:4">
+      <c r="D68" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="4:4">
-      <c r="D68" s="1" t="s">
+    <row r="69" spans="4:4">
+      <c r="D69" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="4:4">
-      <c r="D69" s="1" t="s">
+    <row r="70" spans="4:4">
+      <c r="D70" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="4:4">
-      <c r="D70" s="1" t="s">
+    <row r="71" spans="4:4">
+      <c r="D71" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="4:4">
-      <c r="D71" s="1" t="s">
+    <row r="72" spans="4:4">
+      <c r="D72" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="4:4">
-      <c r="D72" s="1" t="s">
+    <row r="73" spans="4:4">
+      <c r="D73" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="4:4">
-      <c r="D73" s="1" t="s">
+    <row r="74" spans="4:4">
+      <c r="D74" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="4:4">
-      <c r="D74" s="1" t="s">
+    <row r="75" spans="4:4">
+      <c r="D75" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="4:4">
-      <c r="D75" s="1" t="s">
+    <row r="76" spans="4:4">
+      <c r="D76" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="4:4">
-      <c r="D76" s="1" t="s">
+    <row r="77" spans="4:4">
+      <c r="D77" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="4:4">
-      <c r="D77" s="1" t="s">
+    <row r="78" spans="4:4">
+      <c r="D78" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="4:4">
-      <c r="D78" s="1" t="s">
+    <row r="79" spans="4:4">
+      <c r="D79" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="4:4">
-      <c r="D79" s="1" t="s">
+    <row r="80" spans="4:4">
+      <c r="D80" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="80" spans="4:4">
-      <c r="D80" s="1" t="s">
+    <row r="81" spans="4:4">
+      <c r="D81" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="4:4">
-      <c r="D81" s="1" t="s">
+    <row r="82" spans="4:4">
+      <c r="D82" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="4:4">
-      <c r="D82" s="1" t="s">
+    <row r="83" spans="4:4">
+      <c r="D83" s="1" t="s">
         <v>80</v>
       </c>
     </row>

--- a/metadata_dra.xlsx
+++ b/metadata_dra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml-dra161\submission-excel2xml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9D3DD2-74E6-4603-8945-46BA4953A919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B88277A-999E-417F-9076-AF8B49A46C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="674" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -420,7 +420,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="225">
   <si>
     <t>Library Source</t>
   </si>
@@ -1082,11 +1082,59 @@
     <t>Sentosa SQ301</t>
   </si>
   <si>
-    <t>v3.2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2025-06-23 Bioinformation and DDBJ Center</t>
+    <t>v3.3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2026-02-24 Bioinformation and DDBJ Center</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X Plus</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina MiSeq i100</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina MiSeq i100 Plus</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CycloneSEQ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DNBSEQ-T1+</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SURFSeq 5000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SURFSeq Q</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Saluseq Nimbo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Salus Pro</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Salus EVO</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>G-seq500</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>G4</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1711,7 +1759,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DF0F4F9-0E4E-4ABA-B02F-964432F322D9}">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$82</xm:f>
+            <xm:f>Admin!$D$2:$D$94</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I3000</xm:sqref>
         </x14:dataValidation>
@@ -1870,7 +1918,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2203,8 +2251,8 @@
       <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>163</v>
+      <c r="D16" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -2219,8 +2267,8 @@
       <c r="C17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>114</v>
+      <c r="D17" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2236,7 +2284,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2252,7 +2300,7 @@
         <v>54</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2268,7 +2316,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2283,8 +2331,8 @@
       <c r="C21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>151</v>
+      <c r="D21" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2300,7 +2348,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -2316,7 +2364,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2332,7 +2380,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2348,7 +2396,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2364,7 +2412,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -2380,7 +2428,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -2396,7 +2444,7 @@
         <v>78</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2412,7 +2460,7 @@
         <v>146</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2428,7 +2476,7 @@
         <v>81</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2441,8 +2489,8 @@
       <c r="C31" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>90</v>
+      <c r="D31" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2456,7 +2504,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2470,7 +2518,7 @@
         <v>85</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2484,7 +2532,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2497,8 +2545,8 @@
       <c r="C35" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>199</v>
+      <c r="D35" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2512,7 +2560,7 @@
         <v>110</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2526,7 +2574,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>201</v>
+        <v>91</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2540,7 +2588,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2552,7 +2600,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2564,7 +2612,7 @@
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2572,212 +2620,272 @@
       <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="D41" s="1" t="s">
-        <v>160</v>
+      <c r="D41" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="D42" s="1" t="s">
-        <v>161</v>
+      <c r="D42" s="3" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="D43" s="1" t="s">
-        <v>162</v>
+      <c r="D43" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="D44" s="1" t="s">
-        <v>92</v>
+      <c r="D44" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="D45" s="3" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="D46" s="3" t="s">
-        <v>122</v>
+      <c r="D46" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="D47" s="3" t="s">
-        <v>123</v>
+      <c r="D47" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="4:4">
-      <c r="D50" s="1" t="s">
-        <v>23</v>
+      <c r="D50" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="4:4">
-      <c r="D51" s="1" t="s">
-        <v>27</v>
+      <c r="D51" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="4:4">
-      <c r="D52" s="1" t="s">
-        <v>31</v>
+      <c r="D52" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="1" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="1" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="1" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" s="1" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" s="1" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="1" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="1" t="s">
-        <v>203</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="1" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="1" t="s">
-        <v>205</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="1" t="s">
-        <v>206</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" s="1" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" s="1" t="s">
-        <v>68</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" s="1" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="1" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="1" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="1" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="1" t="s">
-        <v>82</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" s="1" t="s">
-        <v>84</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" s="1" t="s">
-        <v>117</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" s="1" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="1" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" s="1" t="s">
-        <v>65</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" s="1" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="1" t="s">
         <v>80</v>
       </c>
     </row>
